--- a/checklists/Group_D_Week_4_Checklist.xlsx
+++ b/checklists/Group_D_Week_4_Checklist.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tpgtelecom-my.sharepoint.com/personal/bel_zhou_tpgtelecom_com_au/Documents/Documents/UNSW/Week 4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/25a0eabcb09bfda7/Documents/Masters/2026-H5 - Data Science Project/ZZSC9020-Data-Science-Project-Group-D/checklists/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0FFCC7F6-4CBC-464D-B719-E5DD2D78A5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{0FFCC7F6-4CBC-464D-B719-E5DD2D78A5E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E99A5E9A-F63B-47A7-966D-E10D25215244}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="960" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13245" yWindow="675" windowWidth="27645" windowHeight="19485" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 4 Checklist" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Week 4 Checklist'!$1:$5</definedName>
   </definedNames>
   <calcPr calcId="191029" forceFullCalc="1"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="98">
   <si>
     <t>Week 4 Checklist</t>
   </si>
@@ -128,12 +127,6 @@
     <t>Data Engineer / Analyst</t>
   </si>
   <si>
-    <t>Complete Pearson and Spearman correlation analyses for the selected modelling variables.</t>
-  </si>
-  <si>
-    <t>Report coefficients and explain why both measures are relevant.</t>
-  </si>
-  <si>
     <t>Complete cross-correlation analysis between PV changes and demand changes.</t>
   </si>
   <si>
@@ -336,6 +329,9 @@
   </si>
   <si>
     <t>Week 4 teamwork reflection and Week 5 plan</t>
+  </si>
+  <si>
+    <t>☑ Complete</t>
   </si>
 </sst>
 </file>
@@ -355,53 +351,62 @@
       <sz val="22"/>
       <color rgb="FF17365D"/>
       <name val="Aptos Display"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FF00A6A6"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF64748B"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF1F2937"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF17365D"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="20"/>
       <color rgb="FF17365D"/>
       <name val="Aptos Display"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF64748B"/>
       <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -530,8 +535,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Week4Checklist" displayName="Week4Checklist" ref="A5:E32">
-  <autoFilter ref="A5:E32" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Week4Checklist" displayName="Week4Checklist" ref="A5:E31">
+  <autoFilter ref="A5:E31" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Team Member"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Role / Focus"/>
@@ -832,8 +837,8 @@
     <tabColor rgb="FF00A6A6"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="29" customWidth="1"/>
@@ -842,7 +847,7 @@
     <col min="5" max="5" width="49" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="34" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -851,7 +856,7 @@
       <c r="D1" s="10"/>
       <c r="E1" s="10"/>
     </row>
-    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>1</v>
       </c>
@@ -860,7 +865,7 @@
       <c r="D2" s="10"/>
       <c r="E2" s="10"/>
     </row>
-    <row r="3" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
@@ -869,7 +874,7 @@
       <c r="D3" s="10"/>
       <c r="E3" s="10"/>
     </row>
-    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -886,7 +891,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -903,7 +908,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>8</v>
       </c>
@@ -920,7 +925,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
@@ -937,7 +942,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -954,7 +959,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>8</v>
       </c>
@@ -971,7 +976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
@@ -988,7 +993,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>8</v>
       </c>
@@ -1005,7 +1010,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
@@ -1022,7 +1027,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1033,13 +1038,13 @@
         <v>29</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -1050,13 +1055,13 @@
         <v>31</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -1067,13 +1072,13 @@
         <v>33</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
@@ -1084,13 +1089,13 @@
         <v>35</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
@@ -1101,13 +1106,13 @@
         <v>37</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -1118,13 +1123,13 @@
         <v>39</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -1135,13 +1140,13 @@
         <v>41</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -1152,13 +1157,13 @@
         <v>43</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -1169,35 +1174,35 @@
         <v>45</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="3" t="s">
+      <c r="B24" s="2" t="s">
         <v>48</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>51</v>
@@ -1209,12 +1214,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>53</v>
@@ -1226,12 +1231,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>55</v>
@@ -1243,12 +1248,12 @@
         <v>56</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>57</v>
@@ -1260,12 +1265,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>59</v>
@@ -1277,12 +1282,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>61</v>
@@ -1294,12 +1299,12 @@
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>63</v>
@@ -1311,12 +1316,12 @@
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>65</v>
@@ -1328,109 +1333,92 @@
         <v>66</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="46" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C32" s="3" t="s">
+    <row r="34" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="D32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="3" t="s">
+      <c r="B34" s="10"/>
+      <c r="C34" s="10"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B35" s="5" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" ht="16" x14ac:dyDescent="0.4">
-      <c r="A35" s="12" t="s">
+      <c r="C35" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B36" s="5" t="s">
+      <c r="D35" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="E35" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D36" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="7">
+        <f>COUNTIF($A$6:$A$31,A36)</f>
+        <v>8</v>
+      </c>
+      <c r="C36" s="7">
+        <f>COUNTIFS($A$6:$A$31,A36,$D$6:$D$31,"☑ Complete")</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="7">
+        <f>COUNTIFS($A$6:$A$31,A36,$D$6:$D$31,"◐ In progress")</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="7">
+        <f>COUNTIFS($A$6:$A$31,A36,$D$6:$D$31,"⚠ Blocked")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B37" s="7">
-        <f>COUNTIF($A$6:$A$32,A37)</f>
-        <v>8</v>
+        <f>COUNTIF($A$6:$A$31,A37)</f>
+        <v>9</v>
       </c>
       <c r="C37" s="7">
-        <f>COUNTIFS($A$6:$A$32,A37,$D$6:$D$32,"☑ Complete")</f>
+        <f>COUNTIFS($A$6:$A$31,A37,$D$6:$D$31,"☑ Complete")</f>
+        <v>9</v>
+      </c>
+      <c r="D37" s="7">
+        <f>COUNTIFS($A$6:$A$31,A37,$D$6:$D$31,"◐ In progress")</f>
         <v>0</v>
       </c>
-      <c r="D37" s="7">
-        <f>COUNTIFS($A$6:$A$32,A37,$D$6:$D$32,"◐ In progress")</f>
+      <c r="E37" s="7">
+        <f>COUNTIFS($A$6:$A$31,A37,$D$6:$D$31,"⚠ Blocked")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="7">
-        <f>COUNTIFS($A$6:$A$32,A37,$D$6:$D$32,"⚠ Blocked")</f>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="7">
+        <f>COUNTIF($A$6:$A$31,A38)</f>
+        <v>9</v>
+      </c>
+      <c r="C38" s="7">
+        <f>COUNTIFS($A$6:$A$31,A38,$D$6:$D$31,"☑ Complete")</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B38" s="7">
-        <f>COUNTIF($A$6:$A$32,A38)</f>
-        <v>10</v>
-      </c>
-      <c r="C38" s="7">
-        <f>COUNTIFS($A$6:$A$32,A38,$D$6:$D$32,"☑ Complete")</f>
+      <c r="D38" s="7">
+        <f>COUNTIFS($A$6:$A$31,A38,$D$6:$D$31,"◐ In progress")</f>
         <v>0</v>
       </c>
-      <c r="D38" s="7">
-        <f>COUNTIFS($A$6:$A$32,A38,$D$6:$D$32,"◐ In progress")</f>
-        <v>0</v>
-      </c>
       <c r="E38" s="7">
-        <f>COUNTIFS($A$6:$A$32,A38,$D$6:$D$32,"⚠ Blocked")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B39" s="7">
-        <f>COUNTIF($A$6:$A$32,A39)</f>
-        <v>9</v>
-      </c>
-      <c r="C39" s="7">
-        <f>COUNTIFS($A$6:$A$32,A39,$D$6:$D$32,"☑ Complete")</f>
-        <v>0</v>
-      </c>
-      <c r="D39" s="7">
-        <f>COUNTIFS($A$6:$A$32,A39,$D$6:$D$32,"◐ In progress")</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="7">
-        <f>COUNTIFS($A$6:$A$32,A39,$D$6:$D$32,"⚠ Blocked")</f>
+        <f>COUNTIFS($A$6:$A$31,A38,$D$6:$D$31,"⚠ Blocked")</f>
         <v>0</v>
       </c>
     </row>
@@ -1438,10 +1426,10 @@
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A35:E35"/>
+    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
-  <conditionalFormatting sqref="D6:D32">
+  <conditionalFormatting sqref="D6:D31">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$D6="☑ Complete"</formula>
     </cfRule>
@@ -1453,7 +1441,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="D6:D32" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="D6:D31" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"☐ Not started,◐ In progress,☑ Complete,⚠ Blocked"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1475,7 +1463,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
     <col min="2" max="2" width="26" customWidth="1"/>
@@ -1483,174 +1471,174 @@
     <col min="4" max="4" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:4" ht="32.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
       <c r="D1" s="10"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C4" s="8" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="3" t="s">
+      <c r="C6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B7" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="3"/>
+    </row>
+    <row r="9" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="3"/>
-    </row>
-    <row r="9" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="3" t="s">
+      <c r="C9" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9" s="3"/>
+    </row>
+    <row r="10" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="3"/>
+    </row>
+    <row r="11" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="3" t="s">
+      <c r="B11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D11" s="3"/>
+    </row>
+    <row r="12" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="3"/>
-    </row>
-    <row r="11" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="C12" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="3"/>
+    </row>
+    <row r="14" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="3"/>
-    </row>
-    <row r="13" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="B14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
+      <c r="C14" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D14" s="3"/>
+    </row>
+    <row r="15" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="3"/>
-    </row>
-    <row r="15" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
+      <c r="C15" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D15" s="3"/>
+    </row>
+    <row r="16" spans="1:4" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="3"/>
-    </row>
-    <row r="16" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="B16" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>11</v>
@@ -1841,15 +1829,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="d64c8698-aed8-482d-9c0d-22767eb66ced">
@@ -1859,14 +1838,47 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CE1D550-B84D-491A-837D-25EF344BF4FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CE1D550-B84D-491A-837D-25EF344BF4FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d64c8698-aed8-482d-9c0d-22767eb66ced"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C52B4B87-E561-4A26-B531-60E3B97758FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F8139B3-66F9-4879-9084-9BA51E577BE2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d64c8698-aed8-482d-9c0d-22767eb66ced"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F8139B3-66F9-4879-9084-9BA51E577BE2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C52B4B87-E561-4A26-B531-60E3B97758FA}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>